--- a/packages/GB Accounts Company 2021-02-28 (Feb21) Excel 2007/expensesform.xlsx
+++ b/packages/GB Accounts Company 2021-02-28 (Feb21) Excel 2007/expensesform.xlsx
@@ -29,7 +29,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Month 01'!$A$1:$H$52</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
